--- a/scenarios/info.xlsx
+++ b/scenarios/info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\OptUncertain\scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A4EBB9-F6CE-4409-96DB-591FC27D4730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DD10D1-9986-468A-A2DC-202C2E672099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>Index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,7 +50,18 @@
     <t>17DRP5sb8fy</t>
   </si>
   <si>
+    <t>1pXnuDYAj8r</t>
+  </si>
+  <si>
     <t>17DRP5sb8fy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 agents 2nd floor, 2 agents 1st floor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1st floor agents find second floor target</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -376,13 +387,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.25" customWidth="1"/>
     <col min="3" max="3" width="12.75" customWidth="1"/>
     <col min="4" max="4" width="12.25" customWidth="1"/>
-    <col min="5" max="5" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="33.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -427,7 +438,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -441,12 +452,61 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/scenarios/info.xlsx
+++ b/scenarios/info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\OptUncertain\scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DD10D1-9986-468A-A2DC-202C2E672099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8951B10C-BB20-435B-8CE8-DFBBC4F947B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2850" yWindow="3555" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1st floor agents find second floor target</t>
+    <t>agents on the stair find second floor target</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/scenarios/info.xlsx
+++ b/scenarios/info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\OptUncertain\scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8951B10C-BB20-435B-8CE8-DFBBC4F947B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376B167D-9491-4375-BE51-FF33B0489317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2850" yWindow="3555" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>Index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,6 +63,9 @@
   <si>
     <t>agents on the stair find second floor target</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29hnd4uzFmX</t>
   </si>
 </sst>
 </file>
@@ -493,15 +496,42 @@
       <c r="A7">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">

--- a/scenarios/info.xlsx
+++ b/scenarios/info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\OptUncertain\scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376B167D-9491-4375-BE51-FF33B0489317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B8DA34-344E-41C0-A8A1-DBE9AFD96763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2850" yWindow="3555" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4875" yWindow="3555" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>29hnd4uzFmX</t>
+    <t>2azQ1b91cZZ</t>
   </si>
 </sst>
 </file>
@@ -514,7 +514,7 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
